--- a/Day10/matrixes.xlsx
+++ b/Day10/matrixes.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e03748fe74b2749e/Projetos/AdventOfCode2025/AdventOfCode2025/Day9/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e03748fe74b2749e/Projetos/AdventOfCode2025/AdventOfCode2025/Day10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="807" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{885717BE-6FC7-4BDE-BD1C-7D6C5A0064BD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1 (2)" sheetId="5" r:id="rId2"/>
+    <sheet name="Planilha1 (3)" sheetId="6" r:id="rId3"/>
+    <sheet name="Planilha1 (4)" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="21">
   <si>
     <t>b0</t>
   </si>
@@ -93,9 +96,6 @@
     <t>x4</t>
   </si>
   <si>
-    <t>x5</t>
-  </si>
-  <si>
     <t>4x6</t>
   </si>
   <si>
@@ -116,12 +116,21 @@
   <si>
     <t>5x1</t>
   </si>
+  <si>
+    <t>6x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>Ñ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,13 +144,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -153,19 +188,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -179,6 +246,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,72 +569,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4253ACB-9502-4D32-A869-2E8DB39FA91E}">
-  <dimension ref="B1:W512"/>
+  <dimension ref="B1:AS512"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="89" width="4.28515625" customWidth="1"/>
+    <col min="1" max="36" width="4.28515625" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" customWidth="1"/>
+    <col min="38" max="40" width="4.28515625" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="89" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
+    </row>
+    <row r="2" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="K2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -572,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -584,47 +653,53 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>0</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -636,100 +711,90 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+    <row r="6" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="7" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="J10" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>7</v>
@@ -738,12 +803,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -753,15 +818,21 @@
       </c>
       <c r="F12" s="1">
         <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="I12" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="J12" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>1</v>
       </c>
@@ -772,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -784,15 +855,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -807,250 +878,224 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
-      <c r="P16" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
+    <row r="15" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U16" s="1" cm="1">
-        <f t="array" ref="U16:U20">MMULT(M16:Q20,S16:S20)</f>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+      <c r="AP16" s="2"/>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2"/>
+    </row>
+    <row r="17" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="2"/>
+    </row>
+    <row r="18" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>10</v>
+      </c>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="2"/>
+    </row>
+    <row r="19" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="W16" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>1</v>
-      </c>
-      <c r="S17" s="1">
+      <c r="I19" s="1">
+        <v>11</v>
+      </c>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="2"/>
+      <c r="AS19" s="2"/>
+    </row>
+    <row r="20" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="1">
+        <v>11</v>
+      </c>
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+    </row>
+    <row r="21" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="1">
         <v>5</v>
       </c>
-      <c r="U17" s="1">
+    </row>
+    <row r="22" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="AO22" s="3"/>
+    </row>
+    <row r="23" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
         <v>5</v>
       </c>
-      <c r="W17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M18" s="1">
-        <v>1</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>1</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
-        <v>12</v>
-      </c>
-      <c r="W18" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M19" s="1">
-        <v>1</v>
-      </c>
-      <c r="N19" s="1">
-        <v>1</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>1</v>
-      </c>
-      <c r="S19" s="1">
-        <v>5</v>
-      </c>
-      <c r="U19" s="1">
-        <v>7</v>
-      </c>
-      <c r="W19" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M20" s="1">
-        <v>1</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>1</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>1</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
+      <c r="AO23" s="3"/>
+    </row>
+    <row r="24" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M22" s="1">
-        <v>1</v>
-      </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>1</v>
-      </c>
-      <c r="P22" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J24" s="1">
-        <f>MDETERM(M22:Q26)</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>1</v>
-      </c>
-      <c r="O24" s="1">
-        <v>1</v>
-      </c>
-      <c r="P24" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>1</v>
-      </c>
-      <c r="O25" s="1">
-        <v>1</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M26" s="1">
-        <v>1</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1">
-        <v>1</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="10:23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="E24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO24" s="3"/>
+    </row>
+    <row r="25" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO25" s="3"/>
+    </row>
+    <row r="26" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO26" s="3"/>
+    </row>
+    <row r="27" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1515,32 +1560,4579 @@
     <row r="494" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="495" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="496" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" spans="9:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B512"/>
+      <c r="C512"/>
+      <c r="D512"/>
+      <c r="E512"/>
+      <c r="F512"/>
+      <c r="G512"/>
       <c r="I512"/>
       <c r="J512"/>
       <c r="K512"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B17:E17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C764131-1371-4089-ABCA-50D9E6D68031}">
+  <dimension ref="A1:AO496"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="36" width="4.28515625" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" customWidth="1"/>
+    <col min="38" max="40" width="4.28515625" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="89" width="4.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2:W5">MMULT(N2:S5,U2:U7)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1">
+        <v>7</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1">
+        <f>MDETERM(B10:G15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO9" s="3"/>
+    </row>
+    <row r="10" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO10" s="3"/>
+    </row>
+    <row r="11" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U24" s="5"/>
+    </row>
+    <row r="25" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B496"/>
+      <c r="C496"/>
+      <c r="D496"/>
+      <c r="E496"/>
+      <c r="F496"/>
+      <c r="G496"/>
+      <c r="I496"/>
+      <c r="J496"/>
+      <c r="K496"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A51B0AB-04D3-43AB-A13F-58A8E12AF684}">
+  <dimension ref="B1:AS504"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="36" width="4.28515625" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" customWidth="1"/>
+    <col min="38" max="40" width="4.28515625" customWidth="1"/>
+    <col min="41" max="41" width="13" style="8" customWidth="1"/>
+    <col min="42" max="89" width="4.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO1" s="3"/>
+    </row>
+    <row r="2" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>2</v>
+      </c>
+      <c r="T2" s="1">
+        <f t="array" ref="T2:T6">MMULT(L2:P6,R2:R6)</f>
+        <v>7</v>
+      </c>
+      <c r="V2" s="1">
+        <v>7</v>
+      </c>
+      <c r="AO2" s="3"/>
+    </row>
+    <row r="3" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>5</v>
+      </c>
+      <c r="T3" s="1">
+        <v>5</v>
+      </c>
+      <c r="V3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="3"/>
+    </row>
+    <row r="4" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="1">
+        <v>12</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>12</v>
+      </c>
+      <c r="V4" s="1">
+        <v>12</v>
+      </c>
+      <c r="AO4" s="3"/>
+    </row>
+    <row r="5" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1">
+        <v>7</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>5</v>
+      </c>
+      <c r="T5" s="1">
+        <v>7</v>
+      </c>
+      <c r="V5" s="1">
+        <v>7</v>
+      </c>
+      <c r="AO5" s="3"/>
+    </row>
+    <row r="6" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AO6" s="3"/>
+    </row>
+    <row r="7" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="3"/>
+    </row>
+    <row r="8" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>7</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1">
+        <v>1</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>7</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>7</v>
+      </c>
+      <c r="AN8" s="2"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="2"/>
+    </row>
+    <row r="9" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>5</v>
+      </c>
+      <c r="S9" s="10">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="10">
+        <v>-1</v>
+      </c>
+      <c r="AC9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="7"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+    </row>
+    <row r="10" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>12</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="7"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2"/>
+      <c r="AS10" s="2"/>
+    </row>
+    <row r="11" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>7</v>
+      </c>
+      <c r="S11" s="10">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="7"/>
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="2"/>
+      <c r="AS11" s="2"/>
+    </row>
+    <row r="12" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2</v>
+      </c>
+      <c r="S12" s="10">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="W12" s="1">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1">
+        <v>-5</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="7"/>
+      <c r="AP12" s="2"/>
+      <c r="AQ12" s="2"/>
+      <c r="AR12" s="2"/>
+      <c r="AS12" s="2"/>
+    </row>
+    <row r="13" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO13" s="3"/>
+    </row>
+    <row r="14" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>7</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>7</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>7</v>
+      </c>
+      <c r="AO14" s="3"/>
+    </row>
+    <row r="15" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>5</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
+      <c r="U15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="3"/>
+    </row>
+    <row r="16" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>5</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>1</v>
+      </c>
+      <c r="W16" s="1">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO16" s="3"/>
+    </row>
+    <row r="17" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>-5</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="10">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="10">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="3"/>
+    </row>
+    <row r="18" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>-5</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="W18" s="1">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1">
+        <v>-5</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="3"/>
+    </row>
+    <row r="19" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO19" s="3"/>
+    </row>
+    <row r="20" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="10">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>2</v>
+      </c>
+      <c r="S20" s="1">
+        <v>1</v>
+      </c>
+      <c r="T20" s="10">
+        <v>0</v>
+      </c>
+      <c r="U20" s="11">
+        <v>1</v>
+      </c>
+      <c r="V20" s="11">
+        <v>0</v>
+      </c>
+      <c r="W20" s="11">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="12">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="1">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AO20" s="3"/>
+    </row>
+    <row r="21" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>5</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>1</v>
+      </c>
+      <c r="U21" s="11">
+        <v>-1</v>
+      </c>
+      <c r="V21" s="11">
+        <v>0</v>
+      </c>
+      <c r="W21" s="11">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="12">
+        <v>-1</v>
+      </c>
+      <c r="AC21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="12">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="3"/>
+    </row>
+    <row r="22" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0</v>
+      </c>
+      <c r="P22" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="11">
+        <v>0</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="3"/>
+    </row>
+    <row r="23" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>5</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>1</v>
+      </c>
+      <c r="W23" s="11">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="12">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3"/>
+    </row>
+    <row r="24" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="11">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
+        <v>0</v>
+      </c>
+      <c r="V24" s="11">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3"/>
+    </row>
+    <row r="25" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO25" s="3"/>
+    </row>
+    <row r="26" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO26" s="3"/>
+    </row>
+    <row r="27" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO27" s="3"/>
+    </row>
+    <row r="28" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO28" s="3"/>
+    </row>
+    <row r="29" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO29" s="3"/>
+    </row>
+    <row r="30" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO30" s="3"/>
+    </row>
+    <row r="31" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO31" s="3"/>
+    </row>
+    <row r="32" spans="12:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO32" s="3"/>
+    </row>
+    <row r="33" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO33" s="3"/>
+    </row>
+    <row r="34" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO34" s="3"/>
+    </row>
+    <row r="35" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO35" s="3"/>
+    </row>
+    <row r="36" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO36" s="3"/>
+    </row>
+    <row r="37" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO37" s="3"/>
+    </row>
+    <row r="38" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO38" s="3"/>
+    </row>
+    <row r="39" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO39" s="3"/>
+    </row>
+    <row r="40" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO40" s="3"/>
+    </row>
+    <row r="41" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO41" s="3"/>
+    </row>
+    <row r="42" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO42" s="3"/>
+    </row>
+    <row r="43" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO43" s="3"/>
+    </row>
+    <row r="44" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO44" s="3"/>
+    </row>
+    <row r="45" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO45" s="3"/>
+    </row>
+    <row r="46" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO46" s="3"/>
+    </row>
+    <row r="47" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO47" s="3"/>
+    </row>
+    <row r="48" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO48" s="3"/>
+    </row>
+    <row r="49" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO49" s="3"/>
+    </row>
+    <row r="50" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO50" s="3"/>
+    </row>
+    <row r="51" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO51" s="3"/>
+    </row>
+    <row r="52" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO52" s="3"/>
+    </row>
+    <row r="53" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO53" s="3"/>
+    </row>
+    <row r="54" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO54" s="3"/>
+    </row>
+    <row r="55" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO55" s="3"/>
+    </row>
+    <row r="56" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO56" s="3"/>
+    </row>
+    <row r="57" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO57" s="3"/>
+    </row>
+    <row r="58" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO58" s="3"/>
+    </row>
+    <row r="59" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO59" s="3"/>
+    </row>
+    <row r="60" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO60" s="3"/>
+    </row>
+    <row r="61" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO61" s="3"/>
+    </row>
+    <row r="62" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO62" s="3"/>
+    </row>
+    <row r="63" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO63" s="3"/>
+    </row>
+    <row r="64" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO64" s="3"/>
+    </row>
+    <row r="65" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO65" s="3"/>
+    </row>
+    <row r="66" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO66" s="3"/>
+    </row>
+    <row r="67" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO67" s="3"/>
+    </row>
+    <row r="68" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO68" s="3"/>
+    </row>
+    <row r="69" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO69" s="3"/>
+    </row>
+    <row r="70" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO70" s="3"/>
+    </row>
+    <row r="71" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO71" s="3"/>
+    </row>
+    <row r="72" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO72" s="3"/>
+    </row>
+    <row r="73" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO73" s="3"/>
+    </row>
+    <row r="74" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO74" s="3"/>
+    </row>
+    <row r="75" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO75" s="3"/>
+    </row>
+    <row r="76" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO76" s="3"/>
+    </row>
+    <row r="77" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO77" s="3"/>
+    </row>
+    <row r="78" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO78" s="3"/>
+    </row>
+    <row r="79" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO79" s="3"/>
+    </row>
+    <row r="80" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO80" s="3"/>
+    </row>
+    <row r="81" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO81" s="3"/>
+    </row>
+    <row r="82" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO82" s="3"/>
+    </row>
+    <row r="83" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO83" s="3"/>
+    </row>
+    <row r="84" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO84" s="3"/>
+    </row>
+    <row r="85" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO85" s="3"/>
+    </row>
+    <row r="86" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO86" s="3"/>
+    </row>
+    <row r="87" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO87" s="3"/>
+    </row>
+    <row r="88" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO88" s="3"/>
+    </row>
+    <row r="89" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO89" s="3"/>
+    </row>
+    <row r="90" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO90" s="3"/>
+    </row>
+    <row r="91" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO91" s="3"/>
+    </row>
+    <row r="92" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO92" s="3"/>
+    </row>
+    <row r="93" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO93" s="3"/>
+    </row>
+    <row r="94" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO94" s="3"/>
+    </row>
+    <row r="95" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO95" s="3"/>
+    </row>
+    <row r="96" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO96" s="3"/>
+    </row>
+    <row r="97" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO97" s="3"/>
+    </row>
+    <row r="98" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO98" s="3"/>
+    </row>
+    <row r="99" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO99" s="3"/>
+    </row>
+    <row r="100" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO100" s="3"/>
+    </row>
+    <row r="101" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO101" s="3"/>
+    </row>
+    <row r="102" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO102" s="3"/>
+    </row>
+    <row r="103" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO103" s="3"/>
+    </row>
+    <row r="104" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO104" s="3"/>
+    </row>
+    <row r="105" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO105" s="3"/>
+    </row>
+    <row r="106" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO106" s="3"/>
+    </row>
+    <row r="107" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO107" s="3"/>
+    </row>
+    <row r="108" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO108" s="3"/>
+    </row>
+    <row r="109" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO109" s="3"/>
+    </row>
+    <row r="110" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO110" s="3"/>
+    </row>
+    <row r="111" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO111" s="3"/>
+    </row>
+    <row r="112" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO112" s="3"/>
+    </row>
+    <row r="113" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO113" s="3"/>
+    </row>
+    <row r="114" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO114" s="3"/>
+    </row>
+    <row r="115" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO115" s="3"/>
+    </row>
+    <row r="116" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO116" s="3"/>
+    </row>
+    <row r="117" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO117" s="3"/>
+    </row>
+    <row r="118" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO118" s="3"/>
+    </row>
+    <row r="119" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO119" s="3"/>
+    </row>
+    <row r="120" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO120" s="3"/>
+    </row>
+    <row r="121" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO121" s="3"/>
+    </row>
+    <row r="122" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO122" s="3"/>
+    </row>
+    <row r="123" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO123" s="3"/>
+    </row>
+    <row r="124" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO124" s="3"/>
+    </row>
+    <row r="125" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO125" s="3"/>
+    </row>
+    <row r="126" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO126" s="3"/>
+    </row>
+    <row r="127" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO127" s="3"/>
+    </row>
+    <row r="128" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO128" s="3"/>
+    </row>
+    <row r="129" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO129" s="3"/>
+    </row>
+    <row r="130" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO130" s="3"/>
+    </row>
+    <row r="131" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO131" s="3"/>
+    </row>
+    <row r="132" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO132" s="3"/>
+    </row>
+    <row r="133" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO133" s="3"/>
+    </row>
+    <row r="134" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO134" s="3"/>
+    </row>
+    <row r="135" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO135" s="3"/>
+    </row>
+    <row r="136" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO136" s="3"/>
+    </row>
+    <row r="137" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO137" s="3"/>
+    </row>
+    <row r="138" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO138" s="3"/>
+    </row>
+    <row r="139" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO139" s="3"/>
+    </row>
+    <row r="140" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO140" s="3"/>
+    </row>
+    <row r="141" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO141" s="3"/>
+    </row>
+    <row r="142" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO142" s="3"/>
+    </row>
+    <row r="143" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO143" s="3"/>
+    </row>
+    <row r="144" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO144" s="3"/>
+    </row>
+    <row r="145" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO145" s="3"/>
+    </row>
+    <row r="146" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO146" s="3"/>
+    </row>
+    <row r="147" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO147" s="3"/>
+    </row>
+    <row r="148" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO148" s="3"/>
+    </row>
+    <row r="149" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO149" s="3"/>
+    </row>
+    <row r="150" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO150" s="3"/>
+    </row>
+    <row r="151" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO151" s="3"/>
+    </row>
+    <row r="152" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO152" s="3"/>
+    </row>
+    <row r="153" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO153" s="3"/>
+    </row>
+    <row r="154" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO154" s="3"/>
+    </row>
+    <row r="155" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO155" s="3"/>
+    </row>
+    <row r="156" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO156" s="3"/>
+    </row>
+    <row r="157" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO157" s="3"/>
+    </row>
+    <row r="158" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO158" s="3"/>
+    </row>
+    <row r="159" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO159" s="3"/>
+    </row>
+    <row r="160" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO160" s="3"/>
+    </row>
+    <row r="161" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO161" s="3"/>
+    </row>
+    <row r="162" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO162" s="3"/>
+    </row>
+    <row r="163" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO163" s="3"/>
+    </row>
+    <row r="164" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO164" s="3"/>
+    </row>
+    <row r="165" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO165" s="3"/>
+    </row>
+    <row r="166" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO166" s="3"/>
+    </row>
+    <row r="167" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO167" s="3"/>
+    </row>
+    <row r="168" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO168" s="3"/>
+    </row>
+    <row r="169" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO169" s="3"/>
+    </row>
+    <row r="170" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO170" s="3"/>
+    </row>
+    <row r="171" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO171" s="3"/>
+    </row>
+    <row r="172" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO172" s="3"/>
+    </row>
+    <row r="173" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO173" s="3"/>
+    </row>
+    <row r="174" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO174" s="3"/>
+    </row>
+    <row r="175" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO175" s="3"/>
+    </row>
+    <row r="176" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO176" s="3"/>
+    </row>
+    <row r="177" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO177" s="3"/>
+    </row>
+    <row r="178" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO178" s="3"/>
+    </row>
+    <row r="179" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO179" s="3"/>
+    </row>
+    <row r="180" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO180" s="3"/>
+    </row>
+    <row r="181" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO181" s="3"/>
+    </row>
+    <row r="182" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO182" s="3"/>
+    </row>
+    <row r="183" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO183" s="3"/>
+    </row>
+    <row r="184" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO184" s="3"/>
+    </row>
+    <row r="185" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO185" s="3"/>
+    </row>
+    <row r="186" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO186" s="3"/>
+    </row>
+    <row r="187" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO187" s="3"/>
+    </row>
+    <row r="188" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO188" s="3"/>
+    </row>
+    <row r="189" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO189" s="3"/>
+    </row>
+    <row r="190" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO190" s="3"/>
+    </row>
+    <row r="191" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO191" s="3"/>
+    </row>
+    <row r="192" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO192" s="3"/>
+    </row>
+    <row r="193" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO193" s="3"/>
+    </row>
+    <row r="194" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO194" s="3"/>
+    </row>
+    <row r="195" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO195" s="3"/>
+    </row>
+    <row r="196" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO196" s="3"/>
+    </row>
+    <row r="197" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO197" s="3"/>
+    </row>
+    <row r="198" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO198" s="3"/>
+    </row>
+    <row r="199" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO199" s="3"/>
+    </row>
+    <row r="200" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO200" s="3"/>
+    </row>
+    <row r="201" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO201" s="3"/>
+    </row>
+    <row r="202" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO202" s="3"/>
+    </row>
+    <row r="203" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO203" s="3"/>
+    </row>
+    <row r="204" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO204" s="3"/>
+    </row>
+    <row r="205" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO205" s="3"/>
+    </row>
+    <row r="206" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO206" s="3"/>
+    </row>
+    <row r="207" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO207" s="3"/>
+    </row>
+    <row r="208" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO208" s="3"/>
+    </row>
+    <row r="209" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO209" s="3"/>
+    </row>
+    <row r="210" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO210" s="3"/>
+    </row>
+    <row r="211" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO211" s="3"/>
+    </row>
+    <row r="212" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO212" s="3"/>
+    </row>
+    <row r="213" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO213" s="3"/>
+    </row>
+    <row r="214" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO214" s="3"/>
+    </row>
+    <row r="215" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO215" s="3"/>
+    </row>
+    <row r="216" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO216" s="3"/>
+    </row>
+    <row r="217" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO217" s="3"/>
+    </row>
+    <row r="218" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO218" s="3"/>
+    </row>
+    <row r="219" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO219" s="3"/>
+    </row>
+    <row r="220" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO220" s="3"/>
+    </row>
+    <row r="221" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO221" s="3"/>
+    </row>
+    <row r="222" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO222" s="3"/>
+    </row>
+    <row r="223" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO223" s="3"/>
+    </row>
+    <row r="224" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO224" s="3"/>
+    </row>
+    <row r="225" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO225" s="3"/>
+    </row>
+    <row r="226" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO226" s="3"/>
+    </row>
+    <row r="227" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO227" s="3"/>
+    </row>
+    <row r="228" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO228" s="3"/>
+    </row>
+    <row r="229" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO229" s="3"/>
+    </row>
+    <row r="230" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO230" s="3"/>
+    </row>
+    <row r="231" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO231" s="3"/>
+    </row>
+    <row r="232" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO232" s="3"/>
+    </row>
+    <row r="233" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO233" s="3"/>
+    </row>
+    <row r="234" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO234" s="3"/>
+    </row>
+    <row r="235" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO235" s="3"/>
+    </row>
+    <row r="236" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO236" s="3"/>
+    </row>
+    <row r="237" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO237" s="3"/>
+    </row>
+    <row r="238" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO238" s="3"/>
+    </row>
+    <row r="239" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO239" s="3"/>
+    </row>
+    <row r="240" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO240" s="3"/>
+    </row>
+    <row r="241" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO241" s="3"/>
+    </row>
+    <row r="242" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO242" s="3"/>
+    </row>
+    <row r="243" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO243" s="3"/>
+    </row>
+    <row r="244" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO244" s="3"/>
+    </row>
+    <row r="245" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO245" s="3"/>
+    </row>
+    <row r="246" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO246" s="3"/>
+    </row>
+    <row r="247" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO247" s="3"/>
+    </row>
+    <row r="248" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO248" s="3"/>
+    </row>
+    <row r="249" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO249" s="3"/>
+    </row>
+    <row r="250" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO250" s="3"/>
+    </row>
+    <row r="251" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO251" s="3"/>
+    </row>
+    <row r="252" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO252" s="3"/>
+    </row>
+    <row r="253" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO253" s="3"/>
+    </row>
+    <row r="254" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO254" s="3"/>
+    </row>
+    <row r="255" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO255" s="3"/>
+    </row>
+    <row r="256" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO256" s="3"/>
+    </row>
+    <row r="257" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO257" s="3"/>
+    </row>
+    <row r="258" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO258" s="3"/>
+    </row>
+    <row r="259" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO259" s="3"/>
+    </row>
+    <row r="260" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO260" s="3"/>
+    </row>
+    <row r="261" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO261" s="3"/>
+    </row>
+    <row r="262" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO262" s="3"/>
+    </row>
+    <row r="263" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO263" s="3"/>
+    </row>
+    <row r="264" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO264" s="3"/>
+    </row>
+    <row r="265" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO265" s="3"/>
+    </row>
+    <row r="266" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO266" s="3"/>
+    </row>
+    <row r="267" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO267" s="3"/>
+    </row>
+    <row r="268" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO268" s="3"/>
+    </row>
+    <row r="269" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO269" s="3"/>
+    </row>
+    <row r="270" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO270" s="3"/>
+    </row>
+    <row r="271" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO271" s="3"/>
+    </row>
+    <row r="272" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO272" s="3"/>
+    </row>
+    <row r="273" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO273" s="3"/>
+    </row>
+    <row r="274" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO274" s="3"/>
+    </row>
+    <row r="275" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO275" s="3"/>
+    </row>
+    <row r="276" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO276" s="3"/>
+    </row>
+    <row r="277" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO277" s="3"/>
+    </row>
+    <row r="278" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO278" s="3"/>
+    </row>
+    <row r="279" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO279" s="3"/>
+    </row>
+    <row r="280" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO280" s="3"/>
+    </row>
+    <row r="281" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO281" s="3"/>
+    </row>
+    <row r="282" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO282" s="3"/>
+    </row>
+    <row r="283" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO283" s="3"/>
+    </row>
+    <row r="284" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO284" s="3"/>
+    </row>
+    <row r="285" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO285" s="3"/>
+    </row>
+    <row r="286" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO286" s="3"/>
+    </row>
+    <row r="287" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO287" s="3"/>
+    </row>
+    <row r="288" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO288" s="3"/>
+    </row>
+    <row r="289" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO289" s="3"/>
+    </row>
+    <row r="290" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO290" s="3"/>
+    </row>
+    <row r="291" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO291" s="3"/>
+    </row>
+    <row r="292" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO292" s="3"/>
+    </row>
+    <row r="293" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO293" s="3"/>
+    </row>
+    <row r="294" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO294" s="3"/>
+    </row>
+    <row r="295" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO295" s="3"/>
+    </row>
+    <row r="296" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO296" s="3"/>
+    </row>
+    <row r="297" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO297" s="3"/>
+    </row>
+    <row r="298" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO298" s="3"/>
+    </row>
+    <row r="299" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO299" s="3"/>
+    </row>
+    <row r="300" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO300" s="3"/>
+    </row>
+    <row r="301" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO301" s="3"/>
+    </row>
+    <row r="302" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO302" s="3"/>
+    </row>
+    <row r="303" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO303" s="3"/>
+    </row>
+    <row r="304" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO304" s="3"/>
+    </row>
+    <row r="305" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO305" s="3"/>
+    </row>
+    <row r="306" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO306" s="3"/>
+    </row>
+    <row r="307" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO307" s="3"/>
+    </row>
+    <row r="308" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO308" s="3"/>
+    </row>
+    <row r="309" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO309" s="3"/>
+    </row>
+    <row r="310" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO310" s="3"/>
+    </row>
+    <row r="311" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO311" s="3"/>
+    </row>
+    <row r="312" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO312" s="3"/>
+    </row>
+    <row r="313" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO313" s="3"/>
+    </row>
+    <row r="314" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO314" s="3"/>
+    </row>
+    <row r="315" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO315" s="3"/>
+    </row>
+    <row r="316" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO316" s="3"/>
+    </row>
+    <row r="317" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO317" s="3"/>
+    </row>
+    <row r="318" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO318" s="3"/>
+    </row>
+    <row r="319" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO319" s="3"/>
+    </row>
+    <row r="320" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO320" s="3"/>
+    </row>
+    <row r="321" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO321" s="3"/>
+    </row>
+    <row r="322" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO322" s="3"/>
+    </row>
+    <row r="323" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO323" s="3"/>
+    </row>
+    <row r="324" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO324" s="3"/>
+    </row>
+    <row r="325" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO325" s="3"/>
+    </row>
+    <row r="326" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO326" s="3"/>
+    </row>
+    <row r="327" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO327" s="3"/>
+    </row>
+    <row r="328" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO328" s="3"/>
+    </row>
+    <row r="329" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO329" s="3"/>
+    </row>
+    <row r="330" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO330" s="3"/>
+    </row>
+    <row r="331" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO331" s="3"/>
+    </row>
+    <row r="332" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO332" s="3"/>
+    </row>
+    <row r="333" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO333" s="3"/>
+    </row>
+    <row r="334" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO334" s="3"/>
+    </row>
+    <row r="335" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO335" s="3"/>
+    </row>
+    <row r="336" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO336" s="3"/>
+    </row>
+    <row r="337" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO337" s="3"/>
+    </row>
+    <row r="338" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO338" s="3"/>
+    </row>
+    <row r="339" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO339" s="3"/>
+    </row>
+    <row r="340" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO340" s="3"/>
+    </row>
+    <row r="341" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO341" s="3"/>
+    </row>
+    <row r="342" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO342" s="3"/>
+    </row>
+    <row r="343" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO343" s="3"/>
+    </row>
+    <row r="344" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO344" s="3"/>
+    </row>
+    <row r="345" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO345" s="3"/>
+    </row>
+    <row r="346" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO346" s="3"/>
+    </row>
+    <row r="347" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO347" s="3"/>
+    </row>
+    <row r="348" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO348" s="3"/>
+    </row>
+    <row r="349" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO349" s="3"/>
+    </row>
+    <row r="350" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO350" s="3"/>
+    </row>
+    <row r="351" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO351" s="3"/>
+    </row>
+    <row r="352" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO352" s="3"/>
+    </row>
+    <row r="353" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO353" s="3"/>
+    </row>
+    <row r="354" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO354" s="3"/>
+    </row>
+    <row r="355" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO355" s="3"/>
+    </row>
+    <row r="356" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO356" s="3"/>
+    </row>
+    <row r="357" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO357" s="3"/>
+    </row>
+    <row r="358" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO358" s="3"/>
+    </row>
+    <row r="359" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO359" s="3"/>
+    </row>
+    <row r="360" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO360" s="3"/>
+    </row>
+    <row r="361" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO361" s="3"/>
+    </row>
+    <row r="362" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO362" s="3"/>
+    </row>
+    <row r="363" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO363" s="3"/>
+    </row>
+    <row r="364" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO364" s="3"/>
+    </row>
+    <row r="365" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO365" s="3"/>
+    </row>
+    <row r="366" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO366" s="3"/>
+    </row>
+    <row r="367" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO367" s="3"/>
+    </row>
+    <row r="368" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO368" s="3"/>
+    </row>
+    <row r="369" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO369" s="3"/>
+    </row>
+    <row r="370" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO370" s="3"/>
+    </row>
+    <row r="371" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO371" s="3"/>
+    </row>
+    <row r="372" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO372" s="3"/>
+    </row>
+    <row r="373" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO373" s="3"/>
+    </row>
+    <row r="374" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO374" s="3"/>
+    </row>
+    <row r="375" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO375" s="3"/>
+    </row>
+    <row r="376" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO376" s="3"/>
+    </row>
+    <row r="377" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO377" s="3"/>
+    </row>
+    <row r="378" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO378" s="3"/>
+    </row>
+    <row r="379" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO379" s="3"/>
+    </row>
+    <row r="380" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO380" s="3"/>
+    </row>
+    <row r="381" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO381" s="3"/>
+    </row>
+    <row r="382" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO382" s="3"/>
+    </row>
+    <row r="383" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO383" s="3"/>
+    </row>
+    <row r="384" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO384" s="3"/>
+    </row>
+    <row r="385" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO385" s="3"/>
+    </row>
+    <row r="386" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO386" s="3"/>
+    </row>
+    <row r="387" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO387" s="3"/>
+    </row>
+    <row r="388" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO388" s="3"/>
+    </row>
+    <row r="389" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO389" s="3"/>
+    </row>
+    <row r="390" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO390" s="3"/>
+    </row>
+    <row r="391" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO391" s="3"/>
+    </row>
+    <row r="392" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO392" s="3"/>
+    </row>
+    <row r="393" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO393" s="3"/>
+    </row>
+    <row r="394" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO394" s="3"/>
+    </row>
+    <row r="395" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO395" s="3"/>
+    </row>
+    <row r="396" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO396" s="3"/>
+    </row>
+    <row r="397" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO397" s="3"/>
+    </row>
+    <row r="398" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO398" s="3"/>
+    </row>
+    <row r="399" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO399" s="3"/>
+    </row>
+    <row r="400" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO400" s="3"/>
+    </row>
+    <row r="401" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO401" s="3"/>
+    </row>
+    <row r="402" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO402" s="3"/>
+    </row>
+    <row r="403" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO403" s="3"/>
+    </row>
+    <row r="404" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO404" s="3"/>
+    </row>
+    <row r="405" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO405" s="3"/>
+    </row>
+    <row r="406" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO406" s="3"/>
+    </row>
+    <row r="407" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO407" s="3"/>
+    </row>
+    <row r="408" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO408" s="3"/>
+    </row>
+    <row r="409" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO409" s="3"/>
+    </row>
+    <row r="410" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO410" s="3"/>
+    </row>
+    <row r="411" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO411" s="3"/>
+    </row>
+    <row r="412" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO412" s="3"/>
+    </row>
+    <row r="413" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO413" s="3"/>
+    </row>
+    <row r="414" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO414" s="3"/>
+    </row>
+    <row r="415" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO415" s="3"/>
+    </row>
+    <row r="416" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO416" s="3"/>
+    </row>
+    <row r="417" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO417" s="3"/>
+    </row>
+    <row r="418" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO418" s="3"/>
+    </row>
+    <row r="419" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO419" s="3"/>
+    </row>
+    <row r="420" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO420" s="3"/>
+    </row>
+    <row r="421" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO421" s="3"/>
+    </row>
+    <row r="422" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO422" s="3"/>
+    </row>
+    <row r="423" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO423" s="3"/>
+    </row>
+    <row r="424" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO424" s="3"/>
+    </row>
+    <row r="425" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO425" s="3"/>
+    </row>
+    <row r="426" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO426" s="3"/>
+    </row>
+    <row r="427" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO427" s="3"/>
+    </row>
+    <row r="428" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO428" s="3"/>
+    </row>
+    <row r="429" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO429" s="3"/>
+    </row>
+    <row r="430" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO430" s="3"/>
+    </row>
+    <row r="431" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO431" s="3"/>
+    </row>
+    <row r="432" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO432" s="3"/>
+    </row>
+    <row r="433" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO433" s="3"/>
+    </row>
+    <row r="434" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO434" s="3"/>
+    </row>
+    <row r="435" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO435" s="3"/>
+    </row>
+    <row r="436" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO436" s="3"/>
+    </row>
+    <row r="437" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO437" s="3"/>
+    </row>
+    <row r="438" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO438" s="3"/>
+    </row>
+    <row r="439" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO439" s="3"/>
+    </row>
+    <row r="440" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO440" s="3"/>
+    </row>
+    <row r="441" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO441" s="3"/>
+    </row>
+    <row r="442" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO442" s="3"/>
+    </row>
+    <row r="443" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO443" s="3"/>
+    </row>
+    <row r="444" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO444" s="3"/>
+    </row>
+    <row r="445" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO445" s="3"/>
+    </row>
+    <row r="446" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO446" s="3"/>
+    </row>
+    <row r="447" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO447" s="3"/>
+    </row>
+    <row r="448" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO448" s="3"/>
+    </row>
+    <row r="449" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO449" s="3"/>
+    </row>
+    <row r="450" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO450" s="3"/>
+    </row>
+    <row r="451" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO451" s="3"/>
+    </row>
+    <row r="452" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO452" s="3"/>
+    </row>
+    <row r="453" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO453" s="3"/>
+    </row>
+    <row r="454" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO454" s="3"/>
+    </row>
+    <row r="455" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO455" s="3"/>
+    </row>
+    <row r="456" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO456" s="3"/>
+    </row>
+    <row r="457" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO457" s="3"/>
+    </row>
+    <row r="458" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO458" s="3"/>
+    </row>
+    <row r="459" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO459" s="3"/>
+    </row>
+    <row r="460" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO460" s="3"/>
+    </row>
+    <row r="461" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO461" s="3"/>
+    </row>
+    <row r="462" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO462" s="3"/>
+    </row>
+    <row r="463" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO463" s="3"/>
+    </row>
+    <row r="464" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO464" s="3"/>
+    </row>
+    <row r="465" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO465" s="3"/>
+    </row>
+    <row r="466" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO466" s="3"/>
+    </row>
+    <row r="467" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO467" s="3"/>
+    </row>
+    <row r="468" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO468" s="3"/>
+    </row>
+    <row r="469" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO469" s="3"/>
+    </row>
+    <row r="470" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO470" s="3"/>
+    </row>
+    <row r="471" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO471" s="3"/>
+    </row>
+    <row r="472" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO472" s="3"/>
+    </row>
+    <row r="473" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO473" s="3"/>
+    </row>
+    <row r="474" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO474" s="3"/>
+    </row>
+    <row r="475" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO475" s="3"/>
+    </row>
+    <row r="476" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO476" s="3"/>
+    </row>
+    <row r="477" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO477" s="3"/>
+    </row>
+    <row r="478" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO478" s="3"/>
+    </row>
+    <row r="479" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO479" s="3"/>
+    </row>
+    <row r="480" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO480" s="3"/>
+    </row>
+    <row r="481" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO481" s="3"/>
+    </row>
+    <row r="482" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO482" s="3"/>
+    </row>
+    <row r="483" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO483" s="3"/>
+    </row>
+    <row r="484" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO484" s="3"/>
+    </row>
+    <row r="485" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO485" s="3"/>
+    </row>
+    <row r="486" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO486" s="3"/>
+    </row>
+    <row r="487" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO487" s="3"/>
+    </row>
+    <row r="488" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO488" s="3"/>
+    </row>
+    <row r="489" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO489" s="3"/>
+    </row>
+    <row r="490" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO490" s="3"/>
+    </row>
+    <row r="491" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO491" s="3"/>
+    </row>
+    <row r="492" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO492" s="3"/>
+    </row>
+    <row r="493" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO493" s="3"/>
+    </row>
+    <row r="494" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO494" s="3"/>
+    </row>
+    <row r="495" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO495" s="3"/>
+    </row>
+    <row r="496" spans="41:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO496" s="3"/>
+    </row>
+    <row r="497" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO497" s="3"/>
+    </row>
+    <row r="498" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO498" s="3"/>
+    </row>
+    <row r="499" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO499" s="3"/>
+    </row>
+    <row r="500" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO500" s="3"/>
+    </row>
+    <row r="501" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO501" s="3"/>
+    </row>
+    <row r="502" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO502" s="3"/>
+    </row>
+    <row r="503" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO503" s="3"/>
+    </row>
+    <row r="504" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B504"/>
+      <c r="C504"/>
+      <c r="D504"/>
+      <c r="E504"/>
+      <c r="F504"/>
+      <c r="G504"/>
+      <c r="I504"/>
+      <c r="J504"/>
+      <c r="K504"/>
+      <c r="AO504" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933C748A-F57E-419A-A335-7369B2990447}">
+  <dimension ref="B1:AS496"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="36" width="4.28515625" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" customWidth="1"/>
+    <col min="38" max="40" width="4.28515625" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="89" width="4.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+    </row>
+    <row r="2" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+    </row>
+    <row r="3" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>11</v>
+      </c>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+    </row>
+    <row r="4" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1">
+        <v>11</v>
+      </c>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+    </row>
+    <row r="5" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="AO6" s="3"/>
+    </row>
+    <row r="7" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="3"/>
+    </row>
+    <row r="8" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO8" s="3"/>
+    </row>
+    <row r="9" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO9" s="3"/>
+    </row>
+    <row r="10" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO10" s="3"/>
+    </row>
+    <row r="11" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B496"/>
+      <c r="C496"/>
+      <c r="D496"/>
+      <c r="E496"/>
+      <c r="F496"/>
+      <c r="G496"/>
+      <c r="I496"/>
+      <c r="J496"/>
+      <c r="K496"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/Day10/matrixes.xlsx
+++ b/Day10/matrixes.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e03748fe74b2749e/Projetos/AdventOfCode2025/AdventOfCode2025/Day10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1034" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A9189C-6015-4D63-BA73-D9F0E2E83A01}"/>
+  <xr:revisionPtr revIDLastSave="1250" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C0F55E1-AA70-4B93-AD86-DFB3DA07BD6C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1 (2)" sheetId="5" r:id="rId2"/>
     <sheet name="Planilha1 (3)" sheetId="6" r:id="rId3"/>
     <sheet name="Planilha1 (4)" sheetId="7" r:id="rId4"/>
+    <sheet name="Planilha2" sheetId="8" r:id="rId5"/>
+    <sheet name="Planilha1 (5)" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="25">
   <si>
     <t>b0</t>
   </si>
@@ -124,6 +126,18 @@
   </si>
   <si>
     <t>t</t>
+  </si>
+  <si>
+    <t>x0 + x3 - x5 = 2</t>
+  </si>
+  <si>
+    <t>x1 + x5 = 5</t>
+  </si>
+  <si>
+    <t>x2 + x3 - x5 = 1</t>
+  </si>
+  <si>
+    <t>x4 + x5 = 3</t>
   </si>
 </sst>
 </file>
@@ -192,7 +206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -227,6 +241,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -243,10 +260,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1596,17 +1609,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C764131-1371-4089-ABCA-50D9E6D68031}">
-  <dimension ref="B1:AO496"/>
+  <dimension ref="B1:AP496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="36" width="4.28515625" customWidth="1"/>
-    <col min="37" max="37" width="4.42578125" customWidth="1"/>
-    <col min="38" max="40" width="4.28515625" customWidth="1"/>
-    <col min="41" max="41" width="13" customWidth="1"/>
-    <col min="42" max="89" width="4.28515625" customWidth="1"/>
+    <col min="1" max="32" width="4.28515625" customWidth="1"/>
+    <col min="33" max="33" width="13.85546875" style="12" customWidth="1"/>
+    <col min="34" max="34" width="5.7109375" style="12" customWidth="1"/>
+    <col min="35" max="37" width="4.28515625" customWidth="1"/>
+    <col min="38" max="38" width="4.42578125" customWidth="1"/>
+    <col min="39" max="41" width="4.28515625" customWidth="1"/>
+    <col min="42" max="42" width="13" customWidth="1"/>
+    <col min="43" max="90" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
@@ -1627,8 +1643,10 @@
       <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+    </row>
+    <row r="2" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>0</v>
       </c>
@@ -1675,14 +1693,13 @@
         <v>1</v>
       </c>
       <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2:W7">MMULT(N2:S7,U2:U7)</f>
+        <f t="array" ref="W2:W5">MMULT(N2:S5,U2:U7)</f>
         <v>3</v>
       </c>
-      <c r="Y2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+    </row>
+    <row r="3" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -1731,11 +1748,10 @@
       <c r="W3" s="1">
         <v>5</v>
       </c>
-      <c r="Y3" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+    </row>
+    <row r="4" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>0</v>
       </c>
@@ -1790,11 +1806,10 @@
       <c r="W4" s="1">
         <v>4</v>
       </c>
-      <c r="Y4" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+    </row>
+    <row r="5" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1843,11 +1858,10 @@
       <c r="W5" s="1">
         <v>7</v>
       </c>
-      <c r="Y5" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+    </row>
+    <row r="6" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1869,81 +1883,118 @@
       <c r="I6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
       <c r="U6" s="1">
         <v>1</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+    </row>
+    <row r="7" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
       <c r="U7" s="1">
         <v>2</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1">
-        <f>MDETERM(B10:G15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AO9" s="3"/>
-    </row>
-    <row r="10" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+    </row>
+    <row r="8" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+    </row>
+    <row r="9" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>7</v>
+      </c>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6"/>
+      <c r="AP9" s="3"/>
+    </row>
+    <row r="10" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>0</v>
       </c>
       <c r="C10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -1952,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1961,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -1970,1124 +2021,2398 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1">
         <v>1</v>
       </c>
       <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AP10" s="3"/>
+    </row>
+    <row r="11" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+    </row>
+    <row r="12" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
         <v>3</v>
       </c>
-      <c r="Q10" s="1">
-        <v>1</v>
-      </c>
-      <c r="R10" s="1">
-        <v>1</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>1</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="1">
-        <v>7</v>
-      </c>
-      <c r="AO10" s="3"/>
-    </row>
-    <row r="11" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+    </row>
+    <row r="13" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+    </row>
+    <row r="14" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>5</v>
       </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>1</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
-        <v>1</v>
-      </c>
-      <c r="W11" s="1">
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="1">
         <v>5</v>
       </c>
-      <c r="Y11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="1">
+      <c r="AG15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1">
-        <v>1</v>
-      </c>
-      <c r="U12" s="1">
-        <v>1</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
-      <c r="U13" s="1">
-        <v>1</v>
-      </c>
-      <c r="V13" s="1">
-        <v>1</v>
-      </c>
-      <c r="W13" s="1">
+      <c r="AJ15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AK16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
         <v>3</v>
       </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="1">
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="AG17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="1">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="1">
         <v>-1</v>
       </c>
-      <c r="H17" s="1">
-        <v>2</v>
-      </c>
-      <c r="J17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5</v>
-      </c>
-      <c r="J18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>4</v>
-      </c>
-      <c r="J19" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>3</v>
-      </c>
-      <c r="J20" s="1">
-        <v>3</v>
-      </c>
-      <c r="L20" s="1">
-        <v>-1</v>
-      </c>
-      <c r="M20" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6"/>
+    </row>
+    <row r="21" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="6"/>
+    </row>
+    <row r="22" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6"/>
+    </row>
+    <row r="23" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+    </row>
+    <row r="24" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="U24" s="5"/>
-    </row>
-    <row r="25" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+    </row>
+    <row r="25" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+    </row>
+    <row r="26" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+    </row>
+    <row r="27" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="6"/>
+    </row>
+    <row r="28" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+    </row>
+    <row r="29" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="6"/>
+    </row>
+    <row r="30" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+    </row>
+    <row r="31" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6"/>
+    </row>
+    <row r="32" spans="2:37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+    </row>
+    <row r="33" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG33" s="6"/>
+      <c r="AH33" s="6"/>
+    </row>
+    <row r="34" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+    </row>
+    <row r="35" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="6"/>
+    </row>
+    <row r="36" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6"/>
+    </row>
+    <row r="37" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG37" s="6"/>
+      <c r="AH37" s="6"/>
+    </row>
+    <row r="38" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG38" s="6"/>
+      <c r="AH38" s="6"/>
+    </row>
+    <row r="39" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG39" s="6"/>
+      <c r="AH39" s="6"/>
+    </row>
+    <row r="40" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG40" s="6"/>
+      <c r="AH40" s="6"/>
+    </row>
+    <row r="41" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="6"/>
+    </row>
+    <row r="42" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6"/>
+    </row>
+    <row r="43" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG43" s="6"/>
+      <c r="AH43" s="6"/>
+    </row>
+    <row r="44" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="6"/>
+    </row>
+    <row r="45" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6"/>
+    </row>
+    <row r="46" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG46" s="6"/>
+      <c r="AH46" s="6"/>
+    </row>
+    <row r="47" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG47" s="6"/>
+      <c r="AH47" s="6"/>
+    </row>
+    <row r="48" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6"/>
+    </row>
+    <row r="49" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG49" s="6"/>
+      <c r="AH49" s="6"/>
+    </row>
+    <row r="50" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG50" s="6"/>
+      <c r="AH50" s="6"/>
+    </row>
+    <row r="51" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6"/>
+    </row>
+    <row r="52" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6"/>
+    </row>
+    <row r="53" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG53" s="6"/>
+      <c r="AH53" s="6"/>
+    </row>
+    <row r="54" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG54" s="6"/>
+      <c r="AH54" s="6"/>
+    </row>
+    <row r="55" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG55" s="6"/>
+      <c r="AH55" s="6"/>
+    </row>
+    <row r="56" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG56" s="6"/>
+      <c r="AH56" s="6"/>
+    </row>
+    <row r="57" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG57" s="6"/>
+      <c r="AH57" s="6"/>
+    </row>
+    <row r="58" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG58" s="6"/>
+      <c r="AH58" s="6"/>
+    </row>
+    <row r="59" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG59" s="6"/>
+      <c r="AH59" s="6"/>
+    </row>
+    <row r="60" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG60" s="6"/>
+      <c r="AH60" s="6"/>
+    </row>
+    <row r="61" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG61" s="6"/>
+      <c r="AH61" s="6"/>
+    </row>
+    <row r="62" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG62" s="6"/>
+      <c r="AH62" s="6"/>
+    </row>
+    <row r="63" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG63" s="6"/>
+      <c r="AH63" s="6"/>
+    </row>
+    <row r="64" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG64" s="6"/>
+      <c r="AH64" s="6"/>
+    </row>
+    <row r="65" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG65" s="6"/>
+      <c r="AH65" s="6"/>
+    </row>
+    <row r="66" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG66" s="6"/>
+      <c r="AH66" s="6"/>
+    </row>
+    <row r="67" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG67" s="6"/>
+      <c r="AH67" s="6"/>
+    </row>
+    <row r="68" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG68" s="6"/>
+      <c r="AH68" s="6"/>
+    </row>
+    <row r="69" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG69" s="6"/>
+      <c r="AH69" s="6"/>
+    </row>
+    <row r="70" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG70" s="6"/>
+      <c r="AH70" s="6"/>
+    </row>
+    <row r="71" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG71" s="6"/>
+      <c r="AH71" s="6"/>
+    </row>
+    <row r="72" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG72" s="6"/>
+      <c r="AH72" s="6"/>
+    </row>
+    <row r="73" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG73" s="6"/>
+      <c r="AH73" s="6"/>
+    </row>
+    <row r="74" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG74" s="6"/>
+      <c r="AH74" s="6"/>
+    </row>
+    <row r="75" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG75" s="6"/>
+      <c r="AH75" s="6"/>
+    </row>
+    <row r="76" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG76" s="6"/>
+      <c r="AH76" s="6"/>
+    </row>
+    <row r="77" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG77" s="6"/>
+      <c r="AH77" s="6"/>
+    </row>
+    <row r="78" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG78" s="6"/>
+      <c r="AH78" s="6"/>
+    </row>
+    <row r="79" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG79" s="6"/>
+      <c r="AH79" s="6"/>
+    </row>
+    <row r="80" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG80" s="6"/>
+      <c r="AH80" s="6"/>
+    </row>
+    <row r="81" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG81" s="6"/>
+      <c r="AH81" s="6"/>
+    </row>
+    <row r="82" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG82" s="6"/>
+      <c r="AH82" s="6"/>
+    </row>
+    <row r="83" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG83" s="6"/>
+      <c r="AH83" s="6"/>
+    </row>
+    <row r="84" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG84" s="6"/>
+      <c r="AH84" s="6"/>
+    </row>
+    <row r="85" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG85" s="6"/>
+      <c r="AH85" s="6"/>
+    </row>
+    <row r="86" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG86" s="6"/>
+      <c r="AH86" s="6"/>
+    </row>
+    <row r="87" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG87" s="6"/>
+      <c r="AH87" s="6"/>
+    </row>
+    <row r="88" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG88" s="6"/>
+      <c r="AH88" s="6"/>
+    </row>
+    <row r="89" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG89" s="6"/>
+      <c r="AH89" s="6"/>
+    </row>
+    <row r="90" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG90" s="6"/>
+      <c r="AH90" s="6"/>
+    </row>
+    <row r="91" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG91" s="6"/>
+      <c r="AH91" s="6"/>
+    </row>
+    <row r="92" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG92" s="6"/>
+      <c r="AH92" s="6"/>
+    </row>
+    <row r="93" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG93" s="6"/>
+      <c r="AH93" s="6"/>
+    </row>
+    <row r="94" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG94" s="6"/>
+      <c r="AH94" s="6"/>
+    </row>
+    <row r="95" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG95" s="6"/>
+      <c r="AH95" s="6"/>
+    </row>
+    <row r="96" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG96" s="6"/>
+      <c r="AH96" s="6"/>
+    </row>
+    <row r="97" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG97" s="6"/>
+      <c r="AH97" s="6"/>
+    </row>
+    <row r="98" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG98" s="6"/>
+      <c r="AH98" s="6"/>
+    </row>
+    <row r="99" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG99" s="6"/>
+      <c r="AH99" s="6"/>
+    </row>
+    <row r="100" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG100" s="6"/>
+      <c r="AH100" s="6"/>
+    </row>
+    <row r="101" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG101" s="6"/>
+      <c r="AH101" s="6"/>
+    </row>
+    <row r="102" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG102" s="6"/>
+      <c r="AH102" s="6"/>
+    </row>
+    <row r="103" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG103" s="6"/>
+      <c r="AH103" s="6"/>
+    </row>
+    <row r="104" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG104" s="6"/>
+      <c r="AH104" s="6"/>
+    </row>
+    <row r="105" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG105" s="6"/>
+      <c r="AH105" s="6"/>
+    </row>
+    <row r="106" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG106" s="6"/>
+      <c r="AH106" s="6"/>
+    </row>
+    <row r="107" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG107" s="6"/>
+      <c r="AH107" s="6"/>
+    </row>
+    <row r="108" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG108" s="6"/>
+      <c r="AH108" s="6"/>
+    </row>
+    <row r="109" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG109" s="6"/>
+      <c r="AH109" s="6"/>
+    </row>
+    <row r="110" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG110" s="6"/>
+      <c r="AH110" s="6"/>
+    </row>
+    <row r="111" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG111" s="6"/>
+      <c r="AH111" s="6"/>
+    </row>
+    <row r="112" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG112" s="6"/>
+      <c r="AH112" s="6"/>
+    </row>
+    <row r="113" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG113" s="6"/>
+      <c r="AH113" s="6"/>
+    </row>
+    <row r="114" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG114" s="6"/>
+      <c r="AH114" s="6"/>
+    </row>
+    <row r="115" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG115" s="6"/>
+      <c r="AH115" s="6"/>
+    </row>
+    <row r="116" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG116" s="6"/>
+      <c r="AH116" s="6"/>
+    </row>
+    <row r="117" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG117" s="6"/>
+      <c r="AH117" s="6"/>
+    </row>
+    <row r="118" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG118" s="6"/>
+      <c r="AH118" s="6"/>
+    </row>
+    <row r="119" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG119" s="6"/>
+      <c r="AH119" s="6"/>
+    </row>
+    <row r="120" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG120" s="6"/>
+      <c r="AH120" s="6"/>
+    </row>
+    <row r="121" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG121" s="6"/>
+      <c r="AH121" s="6"/>
+    </row>
+    <row r="122" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG122" s="6"/>
+      <c r="AH122" s="6"/>
+    </row>
+    <row r="123" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG123" s="6"/>
+      <c r="AH123" s="6"/>
+    </row>
+    <row r="124" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG124" s="6"/>
+      <c r="AH124" s="6"/>
+    </row>
+    <row r="125" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG125" s="6"/>
+      <c r="AH125" s="6"/>
+    </row>
+    <row r="126" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG126" s="6"/>
+      <c r="AH126" s="6"/>
+    </row>
+    <row r="127" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG127" s="6"/>
+      <c r="AH127" s="6"/>
+    </row>
+    <row r="128" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG128" s="6"/>
+      <c r="AH128" s="6"/>
+    </row>
+    <row r="129" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG129" s="6"/>
+      <c r="AH129" s="6"/>
+    </row>
+    <row r="130" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG130" s="6"/>
+      <c r="AH130" s="6"/>
+    </row>
+    <row r="131" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG131" s="6"/>
+      <c r="AH131" s="6"/>
+    </row>
+    <row r="132" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG132" s="6"/>
+      <c r="AH132" s="6"/>
+    </row>
+    <row r="133" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG133" s="6"/>
+      <c r="AH133" s="6"/>
+    </row>
+    <row r="134" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG134" s="6"/>
+      <c r="AH134" s="6"/>
+    </row>
+    <row r="135" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG135" s="6"/>
+      <c r="AH135" s="6"/>
+    </row>
+    <row r="136" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG136" s="6"/>
+      <c r="AH136" s="6"/>
+    </row>
+    <row r="137" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG137" s="6"/>
+      <c r="AH137" s="6"/>
+    </row>
+    <row r="138" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG138" s="6"/>
+      <c r="AH138" s="6"/>
+    </row>
+    <row r="139" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG139" s="6"/>
+      <c r="AH139" s="6"/>
+    </row>
+    <row r="140" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG140" s="6"/>
+      <c r="AH140" s="6"/>
+    </row>
+    <row r="141" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG141" s="6"/>
+      <c r="AH141" s="6"/>
+    </row>
+    <row r="142" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG142" s="6"/>
+      <c r="AH142" s="6"/>
+    </row>
+    <row r="143" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG143" s="6"/>
+      <c r="AH143" s="6"/>
+    </row>
+    <row r="144" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG144" s="6"/>
+      <c r="AH144" s="6"/>
+    </row>
+    <row r="145" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG145" s="6"/>
+      <c r="AH145" s="6"/>
+    </row>
+    <row r="146" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG146" s="6"/>
+      <c r="AH146" s="6"/>
+    </row>
+    <row r="147" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG147" s="6"/>
+      <c r="AH147" s="6"/>
+    </row>
+    <row r="148" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG148" s="6"/>
+      <c r="AH148" s="6"/>
+    </row>
+    <row r="149" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG149" s="6"/>
+      <c r="AH149" s="6"/>
+    </row>
+    <row r="150" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG150" s="6"/>
+      <c r="AH150" s="6"/>
+    </row>
+    <row r="151" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG151" s="6"/>
+      <c r="AH151" s="6"/>
+    </row>
+    <row r="152" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG152" s="6"/>
+      <c r="AH152" s="6"/>
+    </row>
+    <row r="153" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG153" s="6"/>
+      <c r="AH153" s="6"/>
+    </row>
+    <row r="154" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG154" s="6"/>
+      <c r="AH154" s="6"/>
+    </row>
+    <row r="155" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG155" s="6"/>
+      <c r="AH155" s="6"/>
+    </row>
+    <row r="156" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG156" s="6"/>
+      <c r="AH156" s="6"/>
+    </row>
+    <row r="157" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG157" s="6"/>
+      <c r="AH157" s="6"/>
+    </row>
+    <row r="158" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG158" s="6"/>
+      <c r="AH158" s="6"/>
+    </row>
+    <row r="159" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG159" s="6"/>
+      <c r="AH159" s="6"/>
+    </row>
+    <row r="160" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG160" s="6"/>
+      <c r="AH160" s="6"/>
+    </row>
+    <row r="161" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG161" s="6"/>
+      <c r="AH161" s="6"/>
+    </row>
+    <row r="162" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG162" s="6"/>
+      <c r="AH162" s="6"/>
+    </row>
+    <row r="163" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG163" s="6"/>
+      <c r="AH163" s="6"/>
+    </row>
+    <row r="164" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG164" s="6"/>
+      <c r="AH164" s="6"/>
+    </row>
+    <row r="165" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG165" s="6"/>
+      <c r="AH165" s="6"/>
+    </row>
+    <row r="166" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG166" s="6"/>
+      <c r="AH166" s="6"/>
+    </row>
+    <row r="167" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG167" s="6"/>
+      <c r="AH167" s="6"/>
+    </row>
+    <row r="168" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG168" s="6"/>
+      <c r="AH168" s="6"/>
+    </row>
+    <row r="169" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG169" s="6"/>
+      <c r="AH169" s="6"/>
+    </row>
+    <row r="170" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG170" s="6"/>
+      <c r="AH170" s="6"/>
+    </row>
+    <row r="171" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG171" s="6"/>
+      <c r="AH171" s="6"/>
+    </row>
+    <row r="172" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG172" s="6"/>
+      <c r="AH172" s="6"/>
+    </row>
+    <row r="173" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG173" s="6"/>
+      <c r="AH173" s="6"/>
+    </row>
+    <row r="174" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG174" s="6"/>
+      <c r="AH174" s="6"/>
+    </row>
+    <row r="175" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG175" s="6"/>
+      <c r="AH175" s="6"/>
+    </row>
+    <row r="176" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG176" s="6"/>
+      <c r="AH176" s="6"/>
+    </row>
+    <row r="177" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG177" s="6"/>
+      <c r="AH177" s="6"/>
+    </row>
+    <row r="178" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG178" s="6"/>
+      <c r="AH178" s="6"/>
+    </row>
+    <row r="179" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG179" s="6"/>
+      <c r="AH179" s="6"/>
+    </row>
+    <row r="180" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG180" s="6"/>
+      <c r="AH180" s="6"/>
+    </row>
+    <row r="181" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG181" s="6"/>
+      <c r="AH181" s="6"/>
+    </row>
+    <row r="182" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG182" s="6"/>
+      <c r="AH182" s="6"/>
+    </row>
+    <row r="183" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG183" s="6"/>
+      <c r="AH183" s="6"/>
+    </row>
+    <row r="184" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG184" s="6"/>
+      <c r="AH184" s="6"/>
+    </row>
+    <row r="185" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG185" s="6"/>
+      <c r="AH185" s="6"/>
+    </row>
+    <row r="186" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG186" s="6"/>
+      <c r="AH186" s="6"/>
+    </row>
+    <row r="187" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG187" s="6"/>
+      <c r="AH187" s="6"/>
+    </row>
+    <row r="188" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG188" s="6"/>
+      <c r="AH188" s="6"/>
+    </row>
+    <row r="189" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG189" s="6"/>
+      <c r="AH189" s="6"/>
+    </row>
+    <row r="190" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG190" s="6"/>
+      <c r="AH190" s="6"/>
+    </row>
+    <row r="191" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG191" s="6"/>
+      <c r="AH191" s="6"/>
+    </row>
+    <row r="192" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG192" s="6"/>
+      <c r="AH192" s="6"/>
+    </row>
+    <row r="193" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG193" s="6"/>
+      <c r="AH193" s="6"/>
+    </row>
+    <row r="194" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG194" s="6"/>
+      <c r="AH194" s="6"/>
+    </row>
+    <row r="195" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG195" s="6"/>
+      <c r="AH195" s="6"/>
+    </row>
+    <row r="196" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG196" s="6"/>
+      <c r="AH196" s="6"/>
+    </row>
+    <row r="197" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG197" s="6"/>
+      <c r="AH197" s="6"/>
+    </row>
+    <row r="198" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG198" s="6"/>
+      <c r="AH198" s="6"/>
+    </row>
+    <row r="199" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG199" s="6"/>
+      <c r="AH199" s="6"/>
+    </row>
+    <row r="200" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG200" s="6"/>
+      <c r="AH200" s="6"/>
+    </row>
+    <row r="201" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG201" s="6"/>
+      <c r="AH201" s="6"/>
+    </row>
+    <row r="202" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG202" s="6"/>
+      <c r="AH202" s="6"/>
+    </row>
+    <row r="203" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG203" s="6"/>
+      <c r="AH203" s="6"/>
+    </row>
+    <row r="204" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG204" s="6"/>
+      <c r="AH204" s="6"/>
+    </row>
+    <row r="205" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG205" s="6"/>
+      <c r="AH205" s="6"/>
+    </row>
+    <row r="206" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG206" s="6"/>
+      <c r="AH206" s="6"/>
+    </row>
+    <row r="207" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG207" s="6"/>
+      <c r="AH207" s="6"/>
+    </row>
+    <row r="208" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG208" s="6"/>
+      <c r="AH208" s="6"/>
+    </row>
+    <row r="209" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG209" s="6"/>
+      <c r="AH209" s="6"/>
+    </row>
+    <row r="210" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG210" s="6"/>
+      <c r="AH210" s="6"/>
+    </row>
+    <row r="211" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG211" s="6"/>
+      <c r="AH211" s="6"/>
+    </row>
+    <row r="212" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG212" s="6"/>
+      <c r="AH212" s="6"/>
+    </row>
+    <row r="213" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG213" s="6"/>
+      <c r="AH213" s="6"/>
+    </row>
+    <row r="214" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG214" s="6"/>
+      <c r="AH214" s="6"/>
+    </row>
+    <row r="215" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG215" s="6"/>
+      <c r="AH215" s="6"/>
+    </row>
+    <row r="216" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG216" s="6"/>
+      <c r="AH216" s="6"/>
+    </row>
+    <row r="217" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG217" s="6"/>
+      <c r="AH217" s="6"/>
+    </row>
+    <row r="218" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG218" s="6"/>
+      <c r="AH218" s="6"/>
+    </row>
+    <row r="219" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG219" s="6"/>
+      <c r="AH219" s="6"/>
+    </row>
+    <row r="220" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG220" s="6"/>
+      <c r="AH220" s="6"/>
+    </row>
+    <row r="221" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG221" s="6"/>
+      <c r="AH221" s="6"/>
+    </row>
+    <row r="222" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG222" s="6"/>
+      <c r="AH222" s="6"/>
+    </row>
+    <row r="223" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG223" s="6"/>
+      <c r="AH223" s="6"/>
+    </row>
+    <row r="224" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG224" s="6"/>
+      <c r="AH224" s="6"/>
+    </row>
+    <row r="225" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG225" s="6"/>
+      <c r="AH225" s="6"/>
+    </row>
+    <row r="226" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG226" s="6"/>
+      <c r="AH226" s="6"/>
+    </row>
+    <row r="227" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG227" s="6"/>
+      <c r="AH227" s="6"/>
+    </row>
+    <row r="228" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG228" s="6"/>
+      <c r="AH228" s="6"/>
+    </row>
+    <row r="229" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG229" s="6"/>
+      <c r="AH229" s="6"/>
+    </row>
+    <row r="230" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG230" s="6"/>
+      <c r="AH230" s="6"/>
+    </row>
+    <row r="231" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG231" s="6"/>
+      <c r="AH231" s="6"/>
+    </row>
+    <row r="232" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG232" s="6"/>
+      <c r="AH232" s="6"/>
+    </row>
+    <row r="233" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG233" s="6"/>
+      <c r="AH233" s="6"/>
+    </row>
+    <row r="234" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG234" s="6"/>
+      <c r="AH234" s="6"/>
+    </row>
+    <row r="235" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG235" s="6"/>
+      <c r="AH235" s="6"/>
+    </row>
+    <row r="236" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG236" s="6"/>
+      <c r="AH236" s="6"/>
+    </row>
+    <row r="237" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG237" s="6"/>
+      <c r="AH237" s="6"/>
+    </row>
+    <row r="238" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG238" s="6"/>
+      <c r="AH238" s="6"/>
+    </row>
+    <row r="239" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG239" s="6"/>
+      <c r="AH239" s="6"/>
+    </row>
+    <row r="240" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG240" s="6"/>
+      <c r="AH240" s="6"/>
+    </row>
+    <row r="241" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG241" s="6"/>
+      <c r="AH241" s="6"/>
+    </row>
+    <row r="242" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG242" s="6"/>
+      <c r="AH242" s="6"/>
+    </row>
+    <row r="243" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG243" s="6"/>
+      <c r="AH243" s="6"/>
+    </row>
+    <row r="244" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG244" s="6"/>
+      <c r="AH244" s="6"/>
+    </row>
+    <row r="245" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG245" s="6"/>
+      <c r="AH245" s="6"/>
+    </row>
+    <row r="246" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG246" s="6"/>
+      <c r="AH246" s="6"/>
+    </row>
+    <row r="247" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG247" s="6"/>
+      <c r="AH247" s="6"/>
+    </row>
+    <row r="248" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG248" s="6"/>
+      <c r="AH248" s="6"/>
+    </row>
+    <row r="249" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG249" s="6"/>
+      <c r="AH249" s="6"/>
+    </row>
+    <row r="250" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG250" s="6"/>
+      <c r="AH250" s="6"/>
+    </row>
+    <row r="251" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG251" s="6"/>
+      <c r="AH251" s="6"/>
+    </row>
+    <row r="252" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG252" s="6"/>
+      <c r="AH252" s="6"/>
+    </row>
+    <row r="253" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG253" s="6"/>
+      <c r="AH253" s="6"/>
+    </row>
+    <row r="254" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG254" s="6"/>
+      <c r="AH254" s="6"/>
+    </row>
+    <row r="255" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG255" s="6"/>
+      <c r="AH255" s="6"/>
+    </row>
+    <row r="256" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG256" s="6"/>
+      <c r="AH256" s="6"/>
+    </row>
+    <row r="257" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG257" s="6"/>
+      <c r="AH257" s="6"/>
+    </row>
+    <row r="258" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG258" s="6"/>
+      <c r="AH258" s="6"/>
+    </row>
+    <row r="259" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG259" s="6"/>
+      <c r="AH259" s="6"/>
+    </row>
+    <row r="260" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG260" s="6"/>
+      <c r="AH260" s="6"/>
+    </row>
+    <row r="261" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG261" s="6"/>
+      <c r="AH261" s="6"/>
+    </row>
+    <row r="262" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG262" s="6"/>
+      <c r="AH262" s="6"/>
+    </row>
+    <row r="263" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG263" s="6"/>
+      <c r="AH263" s="6"/>
+    </row>
+    <row r="264" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG264" s="6"/>
+      <c r="AH264" s="6"/>
+    </row>
+    <row r="265" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG265" s="6"/>
+      <c r="AH265" s="6"/>
+    </row>
+    <row r="266" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG266" s="6"/>
+      <c r="AH266" s="6"/>
+    </row>
+    <row r="267" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG267" s="6"/>
+      <c r="AH267" s="6"/>
+    </row>
+    <row r="268" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG268" s="6"/>
+      <c r="AH268" s="6"/>
+    </row>
+    <row r="269" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG269" s="6"/>
+      <c r="AH269" s="6"/>
+    </row>
+    <row r="270" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG270" s="6"/>
+      <c r="AH270" s="6"/>
+    </row>
+    <row r="271" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG271" s="6"/>
+      <c r="AH271" s="6"/>
+    </row>
+    <row r="272" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG272" s="6"/>
+      <c r="AH272" s="6"/>
+    </row>
+    <row r="273" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG273" s="6"/>
+      <c r="AH273" s="6"/>
+    </row>
+    <row r="274" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG274" s="6"/>
+      <c r="AH274" s="6"/>
+    </row>
+    <row r="275" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG275" s="6"/>
+      <c r="AH275" s="6"/>
+    </row>
+    <row r="276" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG276" s="6"/>
+      <c r="AH276" s="6"/>
+    </row>
+    <row r="277" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG277" s="6"/>
+      <c r="AH277" s="6"/>
+    </row>
+    <row r="278" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG278" s="6"/>
+      <c r="AH278" s="6"/>
+    </row>
+    <row r="279" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG279" s="6"/>
+      <c r="AH279" s="6"/>
+    </row>
+    <row r="280" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG280" s="6"/>
+      <c r="AH280" s="6"/>
+    </row>
+    <row r="281" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG281" s="6"/>
+      <c r="AH281" s="6"/>
+    </row>
+    <row r="282" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG282" s="6"/>
+      <c r="AH282" s="6"/>
+    </row>
+    <row r="283" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG283" s="6"/>
+      <c r="AH283" s="6"/>
+    </row>
+    <row r="284" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG284" s="6"/>
+      <c r="AH284" s="6"/>
+    </row>
+    <row r="285" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG285" s="6"/>
+      <c r="AH285" s="6"/>
+    </row>
+    <row r="286" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG286" s="6"/>
+      <c r="AH286" s="6"/>
+    </row>
+    <row r="287" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG287" s="6"/>
+      <c r="AH287" s="6"/>
+    </row>
+    <row r="288" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG288" s="6"/>
+      <c r="AH288" s="6"/>
+    </row>
+    <row r="289" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG289" s="6"/>
+      <c r="AH289" s="6"/>
+    </row>
+    <row r="290" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG290" s="6"/>
+      <c r="AH290" s="6"/>
+    </row>
+    <row r="291" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG291" s="6"/>
+      <c r="AH291" s="6"/>
+    </row>
+    <row r="292" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG292" s="6"/>
+      <c r="AH292" s="6"/>
+    </row>
+    <row r="293" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG293" s="6"/>
+      <c r="AH293" s="6"/>
+    </row>
+    <row r="294" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG294" s="6"/>
+      <c r="AH294" s="6"/>
+    </row>
+    <row r="295" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG295" s="6"/>
+      <c r="AH295" s="6"/>
+    </row>
+    <row r="296" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG296" s="6"/>
+      <c r="AH296" s="6"/>
+    </row>
+    <row r="297" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG297" s="6"/>
+      <c r="AH297" s="6"/>
+    </row>
+    <row r="298" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG298" s="6"/>
+      <c r="AH298" s="6"/>
+    </row>
+    <row r="299" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG299" s="6"/>
+      <c r="AH299" s="6"/>
+    </row>
+    <row r="300" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG300" s="6"/>
+      <c r="AH300" s="6"/>
+    </row>
+    <row r="301" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG301" s="6"/>
+      <c r="AH301" s="6"/>
+    </row>
+    <row r="302" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG302" s="6"/>
+      <c r="AH302" s="6"/>
+    </row>
+    <row r="303" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG303" s="6"/>
+      <c r="AH303" s="6"/>
+    </row>
+    <row r="304" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG304" s="6"/>
+      <c r="AH304" s="6"/>
+    </row>
+    <row r="305" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG305" s="6"/>
+      <c r="AH305" s="6"/>
+    </row>
+    <row r="306" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG306" s="6"/>
+      <c r="AH306" s="6"/>
+    </row>
+    <row r="307" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG307" s="6"/>
+      <c r="AH307" s="6"/>
+    </row>
+    <row r="308" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG308" s="6"/>
+      <c r="AH308" s="6"/>
+    </row>
+    <row r="309" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG309" s="6"/>
+      <c r="AH309" s="6"/>
+    </row>
+    <row r="310" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG310" s="6"/>
+      <c r="AH310" s="6"/>
+    </row>
+    <row r="311" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG311" s="6"/>
+      <c r="AH311" s="6"/>
+    </row>
+    <row r="312" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG312" s="6"/>
+      <c r="AH312" s="6"/>
+    </row>
+    <row r="313" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG313" s="6"/>
+      <c r="AH313" s="6"/>
+    </row>
+    <row r="314" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG314" s="6"/>
+      <c r="AH314" s="6"/>
+    </row>
+    <row r="315" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG315" s="6"/>
+      <c r="AH315" s="6"/>
+    </row>
+    <row r="316" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG316" s="6"/>
+      <c r="AH316" s="6"/>
+    </row>
+    <row r="317" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG317" s="6"/>
+      <c r="AH317" s="6"/>
+    </row>
+    <row r="318" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG318" s="6"/>
+      <c r="AH318" s="6"/>
+    </row>
+    <row r="319" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG319" s="6"/>
+      <c r="AH319" s="6"/>
+    </row>
+    <row r="320" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG320" s="6"/>
+      <c r="AH320" s="6"/>
+    </row>
+    <row r="321" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG321" s="6"/>
+      <c r="AH321" s="6"/>
+    </row>
+    <row r="322" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG322" s="6"/>
+      <c r="AH322" s="6"/>
+    </row>
+    <row r="323" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG323" s="6"/>
+      <c r="AH323" s="6"/>
+    </row>
+    <row r="324" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG324" s="6"/>
+      <c r="AH324" s="6"/>
+    </row>
+    <row r="325" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG325" s="6"/>
+      <c r="AH325" s="6"/>
+    </row>
+    <row r="326" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG326" s="6"/>
+      <c r="AH326" s="6"/>
+    </row>
+    <row r="327" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG327" s="6"/>
+      <c r="AH327" s="6"/>
+    </row>
+    <row r="328" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG328" s="6"/>
+      <c r="AH328" s="6"/>
+    </row>
+    <row r="329" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG329" s="6"/>
+      <c r="AH329" s="6"/>
+    </row>
+    <row r="330" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG330" s="6"/>
+      <c r="AH330" s="6"/>
+    </row>
+    <row r="331" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG331" s="6"/>
+      <c r="AH331" s="6"/>
+    </row>
+    <row r="332" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG332" s="6"/>
+      <c r="AH332" s="6"/>
+    </row>
+    <row r="333" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG333" s="6"/>
+      <c r="AH333" s="6"/>
+    </row>
+    <row r="334" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG334" s="6"/>
+      <c r="AH334" s="6"/>
+    </row>
+    <row r="335" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG335" s="6"/>
+      <c r="AH335" s="6"/>
+    </row>
+    <row r="336" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG336" s="6"/>
+      <c r="AH336" s="6"/>
+    </row>
+    <row r="337" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG337" s="6"/>
+      <c r="AH337" s="6"/>
+    </row>
+    <row r="338" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG338" s="6"/>
+      <c r="AH338" s="6"/>
+    </row>
+    <row r="339" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG339" s="6"/>
+      <c r="AH339" s="6"/>
+    </row>
+    <row r="340" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG340" s="6"/>
+      <c r="AH340" s="6"/>
+    </row>
+    <row r="341" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG341" s="6"/>
+      <c r="AH341" s="6"/>
+    </row>
+    <row r="342" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG342" s="6"/>
+      <c r="AH342" s="6"/>
+    </row>
+    <row r="343" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG343" s="6"/>
+      <c r="AH343" s="6"/>
+    </row>
+    <row r="344" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG344" s="6"/>
+      <c r="AH344" s="6"/>
+    </row>
+    <row r="345" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG345" s="6"/>
+      <c r="AH345" s="6"/>
+    </row>
+    <row r="346" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG346" s="6"/>
+      <c r="AH346" s="6"/>
+    </row>
+    <row r="347" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG347" s="6"/>
+      <c r="AH347" s="6"/>
+    </row>
+    <row r="348" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG348" s="6"/>
+      <c r="AH348" s="6"/>
+    </row>
+    <row r="349" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG349" s="6"/>
+      <c r="AH349" s="6"/>
+    </row>
+    <row r="350" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG350" s="6"/>
+      <c r="AH350" s="6"/>
+    </row>
+    <row r="351" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG351" s="6"/>
+      <c r="AH351" s="6"/>
+    </row>
+    <row r="352" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG352" s="6"/>
+      <c r="AH352" s="6"/>
+    </row>
+    <row r="353" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG353" s="6"/>
+      <c r="AH353" s="6"/>
+    </row>
+    <row r="354" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG354" s="6"/>
+      <c r="AH354" s="6"/>
+    </row>
+    <row r="355" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG355" s="6"/>
+      <c r="AH355" s="6"/>
+    </row>
+    <row r="356" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG356" s="6"/>
+      <c r="AH356" s="6"/>
+    </row>
+    <row r="357" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG357" s="6"/>
+      <c r="AH357" s="6"/>
+    </row>
+    <row r="358" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG358" s="6"/>
+      <c r="AH358" s="6"/>
+    </row>
+    <row r="359" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG359" s="6"/>
+      <c r="AH359" s="6"/>
+    </row>
+    <row r="360" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG360" s="6"/>
+      <c r="AH360" s="6"/>
+    </row>
+    <row r="361" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG361" s="6"/>
+      <c r="AH361" s="6"/>
+    </row>
+    <row r="362" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG362" s="6"/>
+      <c r="AH362" s="6"/>
+    </row>
+    <row r="363" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG363" s="6"/>
+      <c r="AH363" s="6"/>
+    </row>
+    <row r="364" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG364" s="6"/>
+      <c r="AH364" s="6"/>
+    </row>
+    <row r="365" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG365" s="6"/>
+      <c r="AH365" s="6"/>
+    </row>
+    <row r="366" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG366" s="6"/>
+      <c r="AH366" s="6"/>
+    </row>
+    <row r="367" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG367" s="6"/>
+      <c r="AH367" s="6"/>
+    </row>
+    <row r="368" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG368" s="6"/>
+      <c r="AH368" s="6"/>
+    </row>
+    <row r="369" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG369" s="6"/>
+      <c r="AH369" s="6"/>
+    </row>
+    <row r="370" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG370" s="6"/>
+      <c r="AH370" s="6"/>
+    </row>
+    <row r="371" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG371" s="6"/>
+      <c r="AH371" s="6"/>
+    </row>
+    <row r="372" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG372" s="6"/>
+      <c r="AH372" s="6"/>
+    </row>
+    <row r="373" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG373" s="6"/>
+      <c r="AH373" s="6"/>
+    </row>
+    <row r="374" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG374" s="6"/>
+      <c r="AH374" s="6"/>
+    </row>
+    <row r="375" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG375" s="6"/>
+      <c r="AH375" s="6"/>
+    </row>
+    <row r="376" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG376" s="6"/>
+      <c r="AH376" s="6"/>
+    </row>
+    <row r="377" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG377" s="6"/>
+      <c r="AH377" s="6"/>
+    </row>
+    <row r="378" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG378" s="6"/>
+      <c r="AH378" s="6"/>
+    </row>
+    <row r="379" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG379" s="6"/>
+      <c r="AH379" s="6"/>
+    </row>
+    <row r="380" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG380" s="6"/>
+      <c r="AH380" s="6"/>
+    </row>
+    <row r="381" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG381" s="6"/>
+      <c r="AH381" s="6"/>
+    </row>
+    <row r="382" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG382" s="6"/>
+      <c r="AH382" s="6"/>
+    </row>
+    <row r="383" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG383" s="6"/>
+      <c r="AH383" s="6"/>
+    </row>
+    <row r="384" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG384" s="6"/>
+      <c r="AH384" s="6"/>
+    </row>
+    <row r="385" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG385" s="6"/>
+      <c r="AH385" s="6"/>
+    </row>
+    <row r="386" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG386" s="6"/>
+      <c r="AH386" s="6"/>
+    </row>
+    <row r="387" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG387" s="6"/>
+      <c r="AH387" s="6"/>
+    </row>
+    <row r="388" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG388" s="6"/>
+      <c r="AH388" s="6"/>
+    </row>
+    <row r="389" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG389" s="6"/>
+      <c r="AH389" s="6"/>
+    </row>
+    <row r="390" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG390" s="6"/>
+      <c r="AH390" s="6"/>
+    </row>
+    <row r="391" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG391" s="6"/>
+      <c r="AH391" s="6"/>
+    </row>
+    <row r="392" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG392" s="6"/>
+      <c r="AH392" s="6"/>
+    </row>
+    <row r="393" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG393" s="6"/>
+      <c r="AH393" s="6"/>
+    </row>
+    <row r="394" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG394" s="6"/>
+      <c r="AH394" s="6"/>
+    </row>
+    <row r="395" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG395" s="6"/>
+      <c r="AH395" s="6"/>
+    </row>
+    <row r="396" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG396" s="6"/>
+      <c r="AH396" s="6"/>
+    </row>
+    <row r="397" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG397" s="6"/>
+      <c r="AH397" s="6"/>
+    </row>
+    <row r="398" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG398" s="6"/>
+      <c r="AH398" s="6"/>
+    </row>
+    <row r="399" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG399" s="6"/>
+      <c r="AH399" s="6"/>
+    </row>
+    <row r="400" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG400" s="6"/>
+      <c r="AH400" s="6"/>
+    </row>
+    <row r="401" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG401" s="6"/>
+      <c r="AH401" s="6"/>
+    </row>
+    <row r="402" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG402" s="6"/>
+      <c r="AH402" s="6"/>
+    </row>
+    <row r="403" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG403" s="6"/>
+      <c r="AH403" s="6"/>
+    </row>
+    <row r="404" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG404" s="6"/>
+      <c r="AH404" s="6"/>
+    </row>
+    <row r="405" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG405" s="6"/>
+      <c r="AH405" s="6"/>
+    </row>
+    <row r="406" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG406" s="6"/>
+      <c r="AH406" s="6"/>
+    </row>
+    <row r="407" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG407" s="6"/>
+      <c r="AH407" s="6"/>
+    </row>
+    <row r="408" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG408" s="6"/>
+      <c r="AH408" s="6"/>
+    </row>
+    <row r="409" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG409" s="6"/>
+      <c r="AH409" s="6"/>
+    </row>
+    <row r="410" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG410" s="6"/>
+      <c r="AH410" s="6"/>
+    </row>
+    <row r="411" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG411" s="6"/>
+      <c r="AH411" s="6"/>
+    </row>
+    <row r="412" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG412" s="6"/>
+      <c r="AH412" s="6"/>
+    </row>
+    <row r="413" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG413" s="6"/>
+      <c r="AH413" s="6"/>
+    </row>
+    <row r="414" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG414" s="6"/>
+      <c r="AH414" s="6"/>
+    </row>
+    <row r="415" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG415" s="6"/>
+      <c r="AH415" s="6"/>
+    </row>
+    <row r="416" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG416" s="6"/>
+      <c r="AH416" s="6"/>
+    </row>
+    <row r="417" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG417" s="6"/>
+      <c r="AH417" s="6"/>
+    </row>
+    <row r="418" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG418" s="6"/>
+      <c r="AH418" s="6"/>
+    </row>
+    <row r="419" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG419" s="6"/>
+      <c r="AH419" s="6"/>
+    </row>
+    <row r="420" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG420" s="6"/>
+      <c r="AH420" s="6"/>
+    </row>
+    <row r="421" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG421" s="6"/>
+      <c r="AH421" s="6"/>
+    </row>
+    <row r="422" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG422" s="6"/>
+      <c r="AH422" s="6"/>
+    </row>
+    <row r="423" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG423" s="6"/>
+      <c r="AH423" s="6"/>
+    </row>
+    <row r="424" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG424" s="6"/>
+      <c r="AH424" s="6"/>
+    </row>
+    <row r="425" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG425" s="6"/>
+      <c r="AH425" s="6"/>
+    </row>
+    <row r="426" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG426" s="6"/>
+      <c r="AH426" s="6"/>
+    </row>
+    <row r="427" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG427" s="6"/>
+      <c r="AH427" s="6"/>
+    </row>
+    <row r="428" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG428" s="6"/>
+      <c r="AH428" s="6"/>
+    </row>
+    <row r="429" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG429" s="6"/>
+      <c r="AH429" s="6"/>
+    </row>
+    <row r="430" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG430" s="6"/>
+      <c r="AH430" s="6"/>
+    </row>
+    <row r="431" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG431" s="6"/>
+      <c r="AH431" s="6"/>
+    </row>
+    <row r="432" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG432" s="6"/>
+      <c r="AH432" s="6"/>
+    </row>
+    <row r="433" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG433" s="6"/>
+      <c r="AH433" s="6"/>
+    </row>
+    <row r="434" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG434" s="6"/>
+      <c r="AH434" s="6"/>
+    </row>
+    <row r="435" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG435" s="6"/>
+      <c r="AH435" s="6"/>
+    </row>
+    <row r="436" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG436" s="6"/>
+      <c r="AH436" s="6"/>
+    </row>
+    <row r="437" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG437" s="6"/>
+      <c r="AH437" s="6"/>
+    </row>
+    <row r="438" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG438" s="6"/>
+      <c r="AH438" s="6"/>
+    </row>
+    <row r="439" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG439" s="6"/>
+      <c r="AH439" s="6"/>
+    </row>
+    <row r="440" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG440" s="6"/>
+      <c r="AH440" s="6"/>
+    </row>
+    <row r="441" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG441" s="6"/>
+      <c r="AH441" s="6"/>
+    </row>
+    <row r="442" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG442" s="6"/>
+      <c r="AH442" s="6"/>
+    </row>
+    <row r="443" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG443" s="6"/>
+      <c r="AH443" s="6"/>
+    </row>
+    <row r="444" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG444" s="6"/>
+      <c r="AH444" s="6"/>
+    </row>
+    <row r="445" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG445" s="6"/>
+      <c r="AH445" s="6"/>
+    </row>
+    <row r="446" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG446" s="6"/>
+      <c r="AH446" s="6"/>
+    </row>
+    <row r="447" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG447" s="6"/>
+      <c r="AH447" s="6"/>
+    </row>
+    <row r="448" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG448" s="6"/>
+      <c r="AH448" s="6"/>
+    </row>
+    <row r="449" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG449" s="6"/>
+      <c r="AH449" s="6"/>
+    </row>
+    <row r="450" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG450" s="6"/>
+      <c r="AH450" s="6"/>
+    </row>
+    <row r="451" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG451" s="6"/>
+      <c r="AH451" s="6"/>
+    </row>
+    <row r="452" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG452" s="6"/>
+      <c r="AH452" s="6"/>
+    </row>
+    <row r="453" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG453" s="6"/>
+      <c r="AH453" s="6"/>
+    </row>
+    <row r="454" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG454" s="6"/>
+      <c r="AH454" s="6"/>
+    </row>
+    <row r="455" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG455" s="6"/>
+      <c r="AH455" s="6"/>
+    </row>
+    <row r="456" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG456" s="6"/>
+      <c r="AH456" s="6"/>
+    </row>
+    <row r="457" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG457" s="6"/>
+      <c r="AH457" s="6"/>
+    </row>
+    <row r="458" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG458" s="6"/>
+      <c r="AH458" s="6"/>
+    </row>
+    <row r="459" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG459" s="6"/>
+      <c r="AH459" s="6"/>
+    </row>
+    <row r="460" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG460" s="6"/>
+      <c r="AH460" s="6"/>
+    </row>
+    <row r="461" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG461" s="6"/>
+      <c r="AH461" s="6"/>
+    </row>
+    <row r="462" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG462" s="6"/>
+      <c r="AH462" s="6"/>
+    </row>
+    <row r="463" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG463" s="6"/>
+      <c r="AH463" s="6"/>
+    </row>
+    <row r="464" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG464" s="6"/>
+      <c r="AH464" s="6"/>
+    </row>
+    <row r="465" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG465" s="6"/>
+      <c r="AH465" s="6"/>
+    </row>
+    <row r="466" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG466" s="6"/>
+      <c r="AH466" s="6"/>
+    </row>
+    <row r="467" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG467" s="6"/>
+      <c r="AH467" s="6"/>
+    </row>
+    <row r="468" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG468" s="6"/>
+      <c r="AH468" s="6"/>
+    </row>
+    <row r="469" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG469" s="6"/>
+      <c r="AH469" s="6"/>
+    </row>
+    <row r="470" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG470" s="6"/>
+      <c r="AH470" s="6"/>
+    </row>
+    <row r="471" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG471" s="6"/>
+      <c r="AH471" s="6"/>
+    </row>
+    <row r="472" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG472" s="6"/>
+      <c r="AH472" s="6"/>
+    </row>
+    <row r="473" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG473" s="6"/>
+      <c r="AH473" s="6"/>
+    </row>
+    <row r="474" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG474" s="6"/>
+      <c r="AH474" s="6"/>
+    </row>
+    <row r="475" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG475" s="6"/>
+      <c r="AH475" s="6"/>
+    </row>
+    <row r="476" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG476" s="6"/>
+      <c r="AH476" s="6"/>
+    </row>
+    <row r="477" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG477" s="6"/>
+      <c r="AH477" s="6"/>
+    </row>
+    <row r="478" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG478" s="6"/>
+      <c r="AH478" s="6"/>
+    </row>
+    <row r="479" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG479" s="6"/>
+      <c r="AH479" s="6"/>
+    </row>
+    <row r="480" spans="33:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG480" s="6"/>
+      <c r="AH480" s="6"/>
+    </row>
+    <row r="481" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG481" s="6"/>
+      <c r="AH481" s="6"/>
+    </row>
+    <row r="482" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG482" s="6"/>
+      <c r="AH482" s="6"/>
+    </row>
+    <row r="483" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG483" s="6"/>
+      <c r="AH483" s="6"/>
+    </row>
+    <row r="484" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG484" s="6"/>
+      <c r="AH484" s="6"/>
+    </row>
+    <row r="485" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG485" s="6"/>
+      <c r="AH485" s="6"/>
+    </row>
+    <row r="486" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG486" s="6"/>
+      <c r="AH486" s="6"/>
+    </row>
+    <row r="487" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG487" s="6"/>
+      <c r="AH487" s="6"/>
+    </row>
+    <row r="488" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG488" s="6"/>
+      <c r="AH488" s="6"/>
+    </row>
+    <row r="489" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG489" s="6"/>
+      <c r="AH489" s="6"/>
+    </row>
+    <row r="490" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG490" s="6"/>
+      <c r="AH490" s="6"/>
+    </row>
+    <row r="491" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG491" s="6"/>
+      <c r="AH491" s="6"/>
+    </row>
+    <row r="492" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG492" s="6"/>
+      <c r="AH492" s="6"/>
+    </row>
+    <row r="493" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG493" s="6"/>
+      <c r="AH493" s="6"/>
+    </row>
+    <row r="494" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG494" s="6"/>
+      <c r="AH494" s="6"/>
+    </row>
+    <row r="495" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG495" s="6"/>
+      <c r="AH495" s="6"/>
+    </row>
+    <row r="496" spans="2:34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B496"/>
       <c r="C496"/>
       <c r="D496"/>
@@ -3097,6 +4422,8 @@
       <c r="I496"/>
       <c r="J496"/>
       <c r="K496"/>
+      <c r="AG496" s="6"/>
+      <c r="AH496" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7905,4 +9232,1622 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{186C7AD0-3B8F-4F3F-B043-9BF559D2067C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55B1CD7-26A5-443E-B47E-0311F2D11819}">
+  <dimension ref="B1:AR496"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="36" width="4.28515625" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" customWidth="1"/>
+    <col min="38" max="88" width="4.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+    </row>
+    <row r="2" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1">
+        <v>29</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2:W7">MMULT(N2:S7,U2:U7)</f>
+        <v>29</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>29</v>
+      </c>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+    </row>
+    <row r="3" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1">
+        <v>40</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>40</v>
+      </c>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
+    </row>
+    <row r="4" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1">
+        <v>23</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
+        <v>20</v>
+      </c>
+      <c r="W4" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>23</v>
+      </c>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+    </row>
+    <row r="5" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1">
+        <v>42</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>19</v>
+      </c>
+      <c r="W5" s="1">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="1">
+        <v>39</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>3</v>
+      </c>
+      <c r="W6" s="1">
+        <v>39</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1">
+        <v>52</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1">
+        <v>20</v>
+      </c>
+      <c r="W7" s="1">
+        <v>52</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1">
+        <v>29</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>1</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1">
+        <v>40</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>42</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
+        <v>39</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>17</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>22</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:16" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="2:11" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B496"/>
+      <c r="C496"/>
+      <c r="D496"/>
+      <c r="E496"/>
+      <c r="F496"/>
+      <c r="G496"/>
+      <c r="I496"/>
+      <c r="J496"/>
+      <c r="K496"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>